--- a/Financial Analysis/COIN.xlsx
+++ b/Financial Analysis/COIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8656899-371F-4EB4-8C3B-0A61D9DE356A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9D3741-BAA3-41F1-9B83-897E821C7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4D7A57D7-C14A-49BE-A452-ABD5A8BEC02E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4D7A57D7-C14A-49BE-A452-ABD5A8BEC02E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -232,7 +232,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -756,14 +756,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>170.76</v>
+        <v>269.39999999999998</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45784</v>
@@ -787,7 +787,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>43355.963999999993</v>
+        <v>68400.659999999989</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -829,7 +829,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>39046.16399999999</v>
+        <v>64090.859999999986</v>
       </c>
     </row>
   </sheetData>
@@ -1102,12 +1102,12 @@
         <v>1719.48</v>
       </c>
       <c r="X5" s="9">
-        <f>T5*0.9</f>
-        <v>1304.6399999999999</v>
+        <f>T5*1.2</f>
+        <v>1739.5199999999998</v>
       </c>
       <c r="Y5" s="9">
-        <f>U5*0.85</f>
-        <v>1024.42</v>
+        <f>U5*1.3</f>
+        <v>1566.7600000000002</v>
       </c>
       <c r="Z5" s="9">
         <f>V5*0.9</f>
@@ -1138,47 +1138,47 @@
       </c>
       <c r="AI5" s="9">
         <f>SUM(W5:Z5)</f>
-        <v>6092.98</v>
+        <v>7070.2000000000007</v>
       </c>
       <c r="AJ5" s="9">
         <f>AI5*1.25</f>
-        <v>7616.2249999999995</v>
+        <v>8837.75</v>
       </c>
       <c r="AK5" s="9">
         <f>AJ5*1.14</f>
-        <v>8682.4964999999993</v>
+        <v>10075.035</v>
       </c>
       <c r="AL5" s="9">
         <f>AK5*1.08</f>
-        <v>9377.0962199999994</v>
+        <v>10881.0378</v>
       </c>
       <c r="AM5" s="9">
         <f>AL5*1.06</f>
-        <v>9939.7219932000007</v>
+        <v>11533.900068000001</v>
       </c>
       <c r="AN5" s="9">
         <f>AM5*1.04</f>
-        <v>10337.310872928001</v>
+        <v>11995.256070720001</v>
       </c>
       <c r="AO5" s="9">
         <f>AN5*1.03</f>
-        <v>10647.430199115841</v>
+        <v>12355.113752841602</v>
       </c>
       <c r="AP5" s="9">
         <f t="shared" ref="AP5" si="0">AO5*1.03</f>
-        <v>10966.853105089316</v>
+        <v>12725.767165426851</v>
       </c>
       <c r="AQ5" s="9">
         <f>AP5*1.02</f>
-        <v>11186.190167191102</v>
+        <v>12980.282508735389</v>
       </c>
       <c r="AR5" s="9">
         <f t="shared" ref="AR5:AS5" si="1">AQ5*1.02</f>
-        <v>11409.913970534924</v>
+        <v>13239.888158910097</v>
       </c>
       <c r="AS5" s="9">
         <f t="shared" si="1"/>
-        <v>11638.112249945623</v>
+        <v>13504.685922088298</v>
       </c>
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.3">
@@ -1251,11 +1251,11 @@
       </c>
       <c r="X6" s="4">
         <f t="shared" ref="X6:Z6" si="2">X5-X7</f>
-        <v>182.64959999999996</v>
+        <v>243.53279999999995</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="2"/>
-        <v>143.41880000000003</v>
+        <v>219.34640000000013</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="2"/>
@@ -1286,47 +1286,47 @@
       </c>
       <c r="AI6" s="4">
         <f>SUM(W6:Z6)</f>
-        <v>853.01720000000012</v>
+        <v>989.8280000000002</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" ref="AJ6:AO6" si="3">AJ5-AJ7</f>
-        <v>1066.2714999999998</v>
+        <v>1237.2849999999999</v>
       </c>
       <c r="AK6" s="4">
         <f t="shared" si="3"/>
-        <v>1215.5495099999998</v>
+        <v>1410.5048999999999</v>
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="3"/>
-        <v>1312.7934708000003</v>
+        <v>1523.345292</v>
       </c>
       <c r="AM6" s="4">
         <f t="shared" si="3"/>
-        <v>1391.5610790480005</v>
+        <v>1614.7460095200004</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="3"/>
-        <v>1447.2235222099207</v>
+        <v>1679.3358499008009</v>
       </c>
       <c r="AO6" s="4">
         <f t="shared" si="3"/>
-        <v>1490.640227876218</v>
+        <v>1729.7159253978243</v>
       </c>
       <c r="AP6" s="4">
         <f t="shared" ref="AP6:AS6" si="4">AP5-AP7</f>
-        <v>1535.3594347125036</v>
+        <v>1781.60740315976</v>
       </c>
       <c r="AQ6" s="4">
         <f t="shared" si="4"/>
-        <v>1566.0666234067539</v>
+        <v>1817.2395512229541</v>
       </c>
       <c r="AR6" s="4">
         <f t="shared" si="4"/>
-        <v>1597.3879558748904</v>
+        <v>1853.5843422474136</v>
       </c>
       <c r="AS6" s="4">
         <f t="shared" si="4"/>
-        <v>1629.3357149923868</v>
+        <v>1890.6560290923626</v>
       </c>
     </row>
     <row r="7" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="X7" s="9">
         <f t="shared" ref="X7:Z7" si="7">X5*0.86</f>
-        <v>1121.9903999999999</v>
+        <v>1495.9871999999998</v>
       </c>
       <c r="Y7" s="9">
         <f t="shared" si="7"/>
-        <v>881.00120000000004</v>
+        <v>1347.4136000000001</v>
       </c>
       <c r="Z7" s="9">
         <f t="shared" si="7"/>
@@ -1456,47 +1456,47 @@
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="8"/>
-        <v>5239.9627999999993</v>
+        <v>6080.3720000000003</v>
       </c>
       <c r="AJ7" s="9">
         <f>AJ5*0.86</f>
-        <v>6549.9534999999996</v>
+        <v>7600.4650000000001</v>
       </c>
       <c r="AK7" s="9">
         <f t="shared" ref="AK7:AS7" si="9">AK5*0.86</f>
-        <v>7466.9469899999995</v>
+        <v>8664.5300999999999</v>
       </c>
       <c r="AL7" s="9">
         <f t="shared" si="9"/>
-        <v>8064.3027491999992</v>
+        <v>9357.6925080000001</v>
       </c>
       <c r="AM7" s="9">
         <f t="shared" si="9"/>
-        <v>8548.1609141520003</v>
+        <v>9919.1540584800005</v>
       </c>
       <c r="AN7" s="9">
         <f t="shared" si="9"/>
-        <v>8890.0873507180804</v>
+        <v>10315.9202208192</v>
       </c>
       <c r="AO7" s="9">
         <f t="shared" si="9"/>
-        <v>9156.7899712396229</v>
+        <v>10625.397827443778</v>
       </c>
       <c r="AP7" s="9">
         <f t="shared" si="9"/>
-        <v>9431.4936703768126</v>
+        <v>10944.159762267091</v>
       </c>
       <c r="AQ7" s="9">
         <f t="shared" si="9"/>
-        <v>9620.1235437843479</v>
+        <v>11163.042957512434</v>
       </c>
       <c r="AR7" s="9">
         <f t="shared" si="9"/>
-        <v>9812.526014660034</v>
+        <v>11386.303816662683</v>
       </c>
       <c r="AS7" s="9">
         <f t="shared" si="9"/>
-        <v>10008.776534953236</v>
+        <v>11614.029892995935</v>
       </c>
     </row>
     <row r="8" spans="2:45" x14ac:dyDescent="0.3">
@@ -1717,11 +1717,11 @@
       </c>
       <c r="X9" s="4">
         <f>X5*0.12</f>
-        <v>156.55679999999998</v>
+        <v>208.74239999999998</v>
       </c>
       <c r="Y9" s="4">
         <f>Y5*0.13</f>
-        <v>133.17460000000003</v>
+        <v>203.67880000000002</v>
       </c>
       <c r="Z9" s="4">
         <f>Z5*0.11</f>
@@ -1752,47 +1752,47 @@
       </c>
       <c r="AI9" s="4">
         <f>SUM(W9:Z9)</f>
-        <v>617.78860000000009</v>
+        <v>740.47839999999997</v>
       </c>
       <c r="AJ9" s="4">
         <f>AJ5*0.09</f>
-        <v>685.46024999999997</v>
+        <v>795.39749999999992</v>
       </c>
       <c r="AK9" s="4">
         <f>AK5*0.09</f>
-        <v>781.42468499999995</v>
+        <v>906.75315000000001</v>
       </c>
       <c r="AL9" s="4">
         <f t="shared" ref="AL9:AS9" si="15">AL5*0.09</f>
-        <v>843.93865979999987</v>
+        <v>979.29340200000001</v>
       </c>
       <c r="AM9" s="4">
         <f t="shared" si="15"/>
-        <v>894.57497938800009</v>
+        <v>1038.05100612</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="15"/>
-        <v>930.35797856352008</v>
+        <v>1079.5730463648001</v>
       </c>
       <c r="AO9" s="4">
         <f t="shared" si="15"/>
-        <v>958.26871792042562</v>
+        <v>1111.9602377557442</v>
       </c>
       <c r="AP9" s="4">
         <f t="shared" si="15"/>
-        <v>987.0167794580384</v>
+        <v>1145.3190448884166</v>
       </c>
       <c r="AQ9" s="4">
         <f t="shared" si="15"/>
-        <v>1006.7571150471991</v>
+        <v>1168.2254257861848</v>
       </c>
       <c r="AR9" s="4">
         <f t="shared" si="15"/>
-        <v>1026.8922573481432</v>
+        <v>1191.5899343019087</v>
       </c>
       <c r="AS9" s="4">
         <f t="shared" si="15"/>
-        <v>1047.430102495106</v>
+        <v>1215.4217329879468</v>
       </c>
     </row>
     <row r="10" spans="2:45" x14ac:dyDescent="0.3">
@@ -2309,11 +2309,11 @@
       </c>
       <c r="X13" s="9">
         <f t="shared" si="23"/>
-        <v>206.19159999999988</v>
+        <v>528.00279999999975</v>
       </c>
       <c r="Y13" s="9">
         <f t="shared" si="23"/>
-        <v>-26.039400000000001</v>
+        <v>369.86880000000008</v>
       </c>
       <c r="Z13" s="9">
         <f t="shared" si="23"/>
@@ -2346,47 +2346,47 @@
       </c>
       <c r="AI13" s="9">
         <f t="shared" si="24"/>
-        <v>1539.0421999999996</v>
+        <v>2256.7616000000007</v>
       </c>
       <c r="AJ13" s="9">
         <f t="shared" si="24"/>
-        <v>2612.4851499999995</v>
+        <v>3553.0594000000001</v>
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="24"/>
-        <v>3303.4338809999999</v>
+        <v>4375.688525999999</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="24"/>
-        <v>3736.8130126799988</v>
+        <v>4894.8480292799995</v>
       </c>
       <c r="AM13" s="9">
         <f t="shared" si="24"/>
-        <v>4082.2419058463993</v>
+        <v>5309.7590234423997</v>
       </c>
       <c r="AN13" s="9">
         <f t="shared" si="24"/>
-        <v>4298.2928740755115</v>
+        <v>5574.9106763753516</v>
       </c>
       <c r="AO13" s="9">
         <f t="shared" si="24"/>
-        <v>4444.6304690379793</v>
+        <v>5759.546805406816</v>
       </c>
       <c r="AP13" s="9">
         <f t="shared" ref="AP13:AS13" si="25">AP7-AP8-AP9-AP10-AP11-AP12</f>
-        <v>4595.7059680241255</v>
+        <v>5950.0697944840258</v>
       </c>
       <c r="AQ13" s="9">
         <f t="shared" si="25"/>
-        <v>4667.2236947689653</v>
+        <v>6048.6747977580671</v>
       </c>
       <c r="AR13" s="9">
         <f t="shared" si="25"/>
-        <v>4739.5598842702339</v>
+        <v>6148.6400093191178</v>
       </c>
       <c r="AS13" s="9">
         <f t="shared" si="25"/>
-        <v>4812.7125490297076</v>
+        <v>6249.9742765795654</v>
       </c>
     </row>
     <row r="14" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2748,43 +2748,43 @@
       </c>
       <c r="AJ16" s="4">
         <f t="shared" ref="AJ16:AO16" si="28">-AI19*0.01</f>
-        <v>-12.367858699999998</v>
+        <v>-18.468473600000006</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="28"/>
-        <v>-20.306664069599996</v>
+        <v>-27.880062988800002</v>
       </c>
       <c r="AL16" s="4">
         <f t="shared" si="28"/>
-        <v>-25.876999560556801</v>
+        <v>-34.515623911910396</v>
       </c>
       <c r="AM16" s="4">
         <f t="shared" si="28"/>
-        <v>-29.367207553924445</v>
+        <v>-38.700596681535281</v>
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="28"/>
-        <v>-32.13653098688259</v>
+        <v>-42.031335040671472</v>
       </c>
       <c r="AO16" s="4">
         <f t="shared" si="28"/>
-        <v>-33.864403062569558</v>
+        <v>-44.156503913398581</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" ref="AP16" si="29">-AO19*0.01</f>
-        <v>-35.025555833536899</v>
+        <v>-45.627223331294225</v>
       </c>
       <c r="AQ16" s="4">
         <f t="shared" ref="AQ16" si="30">-AP19*0.01</f>
-        <v>-36.219376953295786</v>
+        <v>-47.13910090495704</v>
       </c>
       <c r="AR16" s="4">
         <f t="shared" ref="AR16" si="31">-AQ19*0.01</f>
-        <v>-36.776275079085615</v>
+        <v>-47.915241694611716</v>
       </c>
       <c r="AS16" s="4">
         <f t="shared" ref="AS16" si="32">-AR19*0.01</f>
-        <v>-37.333881695261297</v>
+        <v>-48.695634428576575</v>
       </c>
     </row>
     <row r="17" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="X17" s="9">
         <f t="shared" si="35"/>
-        <v>185.19159999999988</v>
+        <v>507.00279999999975</v>
       </c>
       <c r="Y17" s="9">
         <f t="shared" si="35"/>
-        <v>-47.039400000000001</v>
+        <v>348.86880000000008</v>
       </c>
       <c r="Z17" s="9">
         <f t="shared" si="35"/>
@@ -2914,47 +2914,47 @@
       </c>
       <c r="AI17" s="9">
         <f t="shared" si="36"/>
-        <v>1455.0421999999996</v>
+        <v>2172.7616000000007</v>
       </c>
       <c r="AJ17" s="9">
         <f t="shared" si="36"/>
-        <v>2538.3330086999995</v>
+        <v>3485.0078736</v>
       </c>
       <c r="AK17" s="9">
         <f t="shared" si="36"/>
-        <v>3234.6249450696</v>
+        <v>4314.452988988799</v>
       </c>
       <c r="AL17" s="9">
         <f t="shared" si="36"/>
-        <v>3670.9009442405554</v>
+        <v>4837.57458519191</v>
       </c>
       <c r="AM17" s="9">
         <f t="shared" si="36"/>
-        <v>4017.0663733603237</v>
+        <v>5253.9168800839343</v>
       </c>
       <c r="AN17" s="9">
         <f t="shared" si="36"/>
-        <v>4233.050382821194</v>
+        <v>5519.5629891748231</v>
       </c>
       <c r="AO17" s="9">
         <f t="shared" si="36"/>
-        <v>4378.1944791921123</v>
+        <v>5703.4029164117783</v>
       </c>
       <c r="AP17" s="9">
         <f t="shared" si="36"/>
-        <v>4527.4221191619727</v>
+        <v>5892.3876131196303</v>
       </c>
       <c r="AQ17" s="9">
         <f t="shared" si="36"/>
-        <v>4597.0343848857019</v>
+        <v>5989.4052118264644</v>
       </c>
       <c r="AR17" s="9">
         <f t="shared" si="36"/>
-        <v>4666.7352119076622</v>
+        <v>6086.9543035720726</v>
       </c>
       <c r="AS17" s="9">
         <f t="shared" si="36"/>
-        <v>4737.157454860062</v>
+        <v>6185.7809351432352</v>
       </c>
     </row>
     <row r="18" spans="2:162" x14ac:dyDescent="0.3">
@@ -3027,11 +3027,11 @@
       </c>
       <c r="X18" s="4">
         <f t="shared" ref="X18:Z18" si="37">X17*0.15</f>
-        <v>27.778739999999981</v>
+        <v>76.05041999999996</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="37"/>
-        <v>-7.0559099999999999</v>
+        <v>52.330320000000007</v>
       </c>
       <c r="Z18" s="4">
         <f t="shared" si="37"/>
@@ -3062,47 +3062,47 @@
       </c>
       <c r="AI18" s="4">
         <f>SUM(W18:Z18)</f>
-        <v>218.25632999999996</v>
+        <v>325.91423999999995</v>
       </c>
       <c r="AJ18" s="4">
         <f t="shared" ref="AJ18:AS18" si="38">AJ17*0.2</f>
-        <v>507.66660173999992</v>
+        <v>697.00157472000001</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="38"/>
-        <v>646.92498901392003</v>
+        <v>862.89059779775982</v>
       </c>
       <c r="AL18" s="4">
         <f t="shared" si="38"/>
-        <v>734.18018884811113</v>
+        <v>967.51491703838201</v>
       </c>
       <c r="AM18" s="4">
         <f t="shared" si="38"/>
-        <v>803.41327467206474</v>
+        <v>1050.7833760167869</v>
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="38"/>
-        <v>846.61007656423885</v>
+        <v>1103.9125978349646</v>
       </c>
       <c r="AO18" s="4">
         <f t="shared" si="38"/>
-        <v>875.63889583842251</v>
+        <v>1140.6805832823557</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="38"/>
-        <v>905.48442383239455</v>
+        <v>1178.477522623926</v>
       </c>
       <c r="AQ18" s="4">
         <f t="shared" si="38"/>
-        <v>919.40687697714043</v>
+        <v>1197.8810423652928</v>
       </c>
       <c r="AR18" s="4">
         <f t="shared" si="38"/>
-        <v>933.34704238153245</v>
+        <v>1217.3908607144147</v>
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="38"/>
-        <v>947.4314909720124</v>
+        <v>1237.1561870286471</v>
       </c>
     </row>
     <row r="19" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3195,11 +3195,11 @@
       </c>
       <c r="X19" s="9">
         <f t="shared" si="42"/>
-        <v>157.41285999999991</v>
+        <v>430.95237999999978</v>
       </c>
       <c r="Y19" s="9">
         <f t="shared" si="42"/>
-        <v>-39.983490000000003</v>
+        <v>296.53848000000005</v>
       </c>
       <c r="Z19" s="9">
         <f t="shared" si="42"/>
@@ -3232,515 +3232,515 @@
       </c>
       <c r="AI19" s="9">
         <f t="shared" si="43"/>
-        <v>1236.7858699999997</v>
+        <v>1846.8473600000007</v>
       </c>
       <c r="AJ19" s="9">
         <f t="shared" si="43"/>
-        <v>2030.6664069599997</v>
+        <v>2788.00629888</v>
       </c>
       <c r="AK19" s="9">
         <f t="shared" si="43"/>
-        <v>2587.6999560556801</v>
+        <v>3451.5623911910393</v>
       </c>
       <c r="AL19" s="9">
         <f t="shared" si="43"/>
-        <v>2936.7207553924445</v>
+        <v>3870.059668153528</v>
       </c>
       <c r="AM19" s="9">
         <f t="shared" si="43"/>
-        <v>3213.653098688259</v>
+        <v>4203.1335040671474</v>
       </c>
       <c r="AN19" s="9">
         <f t="shared" si="43"/>
-        <v>3386.4403062569554</v>
+        <v>4415.6503913398583</v>
       </c>
       <c r="AO19" s="9">
         <f t="shared" si="43"/>
-        <v>3502.5555833536901</v>
+        <v>4562.7223331294226</v>
       </c>
       <c r="AP19" s="9">
         <f t="shared" ref="AP19:AS19" si="44">AP17-AP18</f>
-        <v>3621.9376953295782</v>
+        <v>4713.910090495704</v>
       </c>
       <c r="AQ19" s="9">
         <f t="shared" si="44"/>
-        <v>3677.6275079085617</v>
+        <v>4791.5241694611714</v>
       </c>
       <c r="AR19" s="9">
         <f t="shared" si="44"/>
-        <v>3733.3881695261298</v>
+        <v>4869.5634428576577</v>
       </c>
       <c r="AS19" s="9">
         <f t="shared" si="44"/>
-        <v>3789.7259638880496</v>
+        <v>4948.6247481145883</v>
       </c>
       <c r="AT19" s="1">
         <f t="shared" ref="AT19:BY19" si="45">AS19*(1+$AV$25)</f>
-        <v>3751.8287042491693</v>
+        <v>4899.1385006334422</v>
       </c>
       <c r="AU19" s="1">
         <f t="shared" si="45"/>
-        <v>3714.3104172066774</v>
+        <v>4850.1471156271073</v>
       </c>
       <c r="AV19" s="1">
         <f t="shared" si="45"/>
-        <v>3677.1673130346107</v>
+        <v>4801.6456444708365</v>
       </c>
       <c r="AW19" s="1">
         <f t="shared" si="45"/>
-        <v>3640.3956399042645</v>
+        <v>4753.6291880261278</v>
       </c>
       <c r="AX19" s="1">
         <f t="shared" si="45"/>
-        <v>3603.9916835052218</v>
+        <v>4706.0928961458667</v>
       </c>
       <c r="AY19" s="1">
         <f t="shared" si="45"/>
-        <v>3567.9517666701695</v>
+        <v>4659.0319671844081</v>
       </c>
       <c r="AZ19" s="1">
         <f t="shared" si="45"/>
-        <v>3532.2722490034676</v>
+        <v>4612.4416475125636</v>
       </c>
       <c r="BA19" s="1">
         <f t="shared" si="45"/>
-        <v>3496.9495265134328</v>
+        <v>4566.3172310374375</v>
       </c>
       <c r="BB19" s="1">
         <f t="shared" si="45"/>
-        <v>3461.9800312482985</v>
+        <v>4520.6540587270629</v>
       </c>
       <c r="BC19" s="1">
         <f t="shared" si="45"/>
-        <v>3427.3602309358153</v>
+        <v>4475.447518139792</v>
       </c>
       <c r="BD19" s="1">
         <f t="shared" si="45"/>
-        <v>3393.0866286264572</v>
+        <v>4430.6930429583945</v>
       </c>
       <c r="BE19" s="1">
         <f t="shared" si="45"/>
-        <v>3359.1557623401927</v>
+        <v>4386.3861125288104</v>
       </c>
       <c r="BF19" s="1">
         <f t="shared" si="45"/>
-        <v>3325.5642047167908</v>
+        <v>4342.5222514035222</v>
       </c>
       <c r="BG19" s="1">
         <f t="shared" si="45"/>
-        <v>3292.3085626696229</v>
+        <v>4299.0970288894869</v>
       </c>
       <c r="BH19" s="1">
         <f t="shared" si="45"/>
-        <v>3259.3854770429266</v>
+        <v>4256.1060586005924</v>
       </c>
       <c r="BI19" s="1">
         <f t="shared" si="45"/>
-        <v>3226.7916222724971</v>
+        <v>4213.5449980145868</v>
       </c>
       <c r="BJ19" s="1">
         <f t="shared" si="45"/>
-        <v>3194.523706049772</v>
+        <v>4171.4095480344413</v>
       </c>
       <c r="BK19" s="1">
         <f t="shared" si="45"/>
-        <v>3162.5784689892744</v>
+        <v>4129.6954525540968</v>
       </c>
       <c r="BL19" s="1">
         <f t="shared" si="45"/>
-        <v>3130.9526842993814</v>
+        <v>4088.3984980285559</v>
       </c>
       <c r="BM19" s="1">
         <f t="shared" si="45"/>
-        <v>3099.6431574563876</v>
+        <v>4047.5145130482701</v>
       </c>
       <c r="BN19" s="1">
         <f t="shared" si="45"/>
-        <v>3068.6467258818238</v>
+        <v>4007.0393679177873</v>
       </c>
       <c r="BO19" s="1">
         <f t="shared" si="45"/>
-        <v>3037.9602586230058</v>
+        <v>3966.9689742386095</v>
       </c>
       <c r="BP19" s="1">
         <f t="shared" si="45"/>
-        <v>3007.5806560367755</v>
+        <v>3927.2992844962232</v>
       </c>
       <c r="BQ19" s="1">
         <f t="shared" si="45"/>
-        <v>2977.5048494764078</v>
+        <v>3888.0262916512611</v>
       </c>
       <c r="BR19" s="1">
         <f t="shared" si="45"/>
-        <v>2947.7298009816436</v>
+        <v>3849.1460287347486</v>
       </c>
       <c r="BS19" s="1">
         <f t="shared" si="45"/>
-        <v>2918.2525029718272</v>
+        <v>3810.6545684474013</v>
       </c>
       <c r="BT19" s="1">
         <f t="shared" si="45"/>
-        <v>2889.0699779421088</v>
+        <v>3772.5480227629273</v>
       </c>
       <c r="BU19" s="1">
         <f t="shared" si="45"/>
-        <v>2860.1792781626878</v>
+        <v>3734.822542535298</v>
       </c>
       <c r="BV19" s="1">
         <f t="shared" si="45"/>
-        <v>2831.5774853810608</v>
+        <v>3697.4743171099449</v>
       </c>
       <c r="BW19" s="1">
         <f t="shared" si="45"/>
-        <v>2803.2617105272502</v>
+        <v>3660.4995739388455</v>
       </c>
       <c r="BX19" s="1">
         <f t="shared" si="45"/>
-        <v>2775.2290934219777</v>
+        <v>3623.8945781994571</v>
       </c>
       <c r="BY19" s="1">
         <f t="shared" si="45"/>
-        <v>2747.4768024877581</v>
+        <v>3587.6556324174626</v>
       </c>
       <c r="BZ19" s="1">
         <f t="shared" ref="BZ19:DE19" si="46">BY19*(1+$AV$25)</f>
-        <v>2720.0020344628806</v>
+        <v>3551.779076093288</v>
       </c>
       <c r="CA19" s="1">
         <f t="shared" si="46"/>
-        <v>2692.8020141182519</v>
+        <v>3516.2612853323553</v>
       </c>
       <c r="CB19" s="1">
         <f t="shared" si="46"/>
-        <v>2665.8739939770694</v>
+        <v>3481.0986724790318</v>
       </c>
       <c r="CC19" s="1">
         <f t="shared" si="46"/>
-        <v>2639.2152540372986</v>
+        <v>3446.2876857542415</v>
       </c>
       <c r="CD19" s="1">
         <f t="shared" si="46"/>
-        <v>2612.8231014969256</v>
+        <v>3411.8248088966989</v>
       </c>
       <c r="CE19" s="1">
         <f t="shared" si="46"/>
-        <v>2586.6948704819565</v>
+        <v>3377.7065608077319</v>
       </c>
       <c r="CF19" s="1">
         <f t="shared" si="46"/>
-        <v>2560.8279217771369</v>
+        <v>3343.9294951996544</v>
       </c>
       <c r="CG19" s="1">
         <f t="shared" si="46"/>
-        <v>2535.2196425593656</v>
+        <v>3310.4902002476579</v>
       </c>
       <c r="CH19" s="1">
         <f t="shared" si="46"/>
-        <v>2509.8674461337719</v>
+        <v>3277.3852982451813</v>
       </c>
       <c r="CI19" s="1">
         <f t="shared" si="46"/>
-        <v>2484.768771672434</v>
+        <v>3244.6114452627294</v>
       </c>
       <c r="CJ19" s="1">
         <f t="shared" si="46"/>
-        <v>2459.9210839557095</v>
+        <v>3212.1653308101022</v>
       </c>
       <c r="CK19" s="1">
         <f t="shared" si="46"/>
-        <v>2435.3218731161523</v>
+        <v>3180.0436775020012</v>
       </c>
       <c r="CL19" s="1">
         <f t="shared" si="46"/>
-        <v>2410.9686543849907</v>
+        <v>3148.2432407269812</v>
       </c>
       <c r="CM19" s="1">
         <f t="shared" si="46"/>
-        <v>2386.8589678411408</v>
+        <v>3116.7608083197115</v>
       </c>
       <c r="CN19" s="1">
         <f t="shared" si="46"/>
-        <v>2362.9903781627295</v>
+        <v>3085.5932002365143</v>
       </c>
       <c r="CO19" s="1">
         <f t="shared" si="46"/>
-        <v>2339.360474381102</v>
+        <v>3054.7372682341493</v>
       </c>
       <c r="CP19" s="1">
         <f t="shared" si="46"/>
-        <v>2315.966869637291</v>
+        <v>3024.1898955518077</v>
       </c>
       <c r="CQ19" s="1">
         <f t="shared" si="46"/>
-        <v>2292.8072009409179</v>
+        <v>2993.9479965962896</v>
       </c>
       <c r="CR19" s="1">
         <f t="shared" si="46"/>
-        <v>2269.8791289315086</v>
+        <v>2964.0085166303265</v>
       </c>
       <c r="CS19" s="1">
         <f t="shared" si="46"/>
-        <v>2247.1803376421935</v>
+        <v>2934.3684314640232</v>
       </c>
       <c r="CT19" s="1">
         <f t="shared" si="46"/>
-        <v>2224.7085342657715</v>
+        <v>2905.0247471493831</v>
       </c>
       <c r="CU19" s="1">
         <f t="shared" si="46"/>
-        <v>2202.4614489231139</v>
+        <v>2875.9744996778891</v>
       </c>
       <c r="CV19" s="1">
         <f t="shared" si="46"/>
-        <v>2180.4368344338827</v>
+        <v>2847.2147546811102</v>
       </c>
       <c r="CW19" s="1">
         <f t="shared" si="46"/>
-        <v>2158.6324660895439</v>
+        <v>2818.7426071342993</v>
       </c>
       <c r="CX19" s="1">
         <f t="shared" si="46"/>
-        <v>2137.0461414286483</v>
+        <v>2790.5551810629563</v>
       </c>
       <c r="CY19" s="1">
         <f t="shared" si="46"/>
-        <v>2115.6756800143617</v>
+        <v>2762.6496292523266</v>
       </c>
       <c r="CZ19" s="1">
         <f t="shared" si="46"/>
-        <v>2094.5189232142179</v>
+        <v>2735.0231329598032</v>
       </c>
       <c r="DA19" s="1">
         <f t="shared" si="46"/>
-        <v>2073.5737339820757</v>
+        <v>2707.6729016302052</v>
       </c>
       <c r="DB19" s="1">
         <f t="shared" si="46"/>
-        <v>2052.8379966422549</v>
+        <v>2680.596172613903</v>
       </c>
       <c r="DC19" s="1">
         <f t="shared" si="46"/>
-        <v>2032.3096166758323</v>
+        <v>2653.7902108877638</v>
       </c>
       <c r="DD19" s="1">
         <f t="shared" si="46"/>
-        <v>2011.9865205090739</v>
+        <v>2627.2523087788863</v>
       </c>
       <c r="DE19" s="1">
         <f t="shared" si="46"/>
-        <v>1991.8666553039832</v>
+        <v>2600.9797856910973</v>
       </c>
       <c r="DF19" s="1">
         <f t="shared" ref="DF19:EK19" si="47">DE19*(1+$AV$25)</f>
-        <v>1971.9479887509433</v>
+        <v>2574.9699878341862</v>
       </c>
       <c r="DG19" s="1">
         <f t="shared" si="47"/>
-        <v>1952.2285088634339</v>
+        <v>2549.2202879558445</v>
       </c>
       <c r="DH19" s="1">
         <f t="shared" si="47"/>
-        <v>1932.7062237747996</v>
+        <v>2523.7280850762859</v>
       </c>
       <c r="DI19" s="1">
         <f t="shared" si="47"/>
-        <v>1913.3791615370515</v>
+        <v>2498.4908042255229</v>
       </c>
       <c r="DJ19" s="1">
         <f t="shared" si="47"/>
-        <v>1894.245369921681</v>
+        <v>2473.5058961832679</v>
       </c>
       <c r="DK19" s="1">
         <f t="shared" si="47"/>
-        <v>1875.3029162224641</v>
+        <v>2448.7708372214352</v>
       </c>
       <c r="DL19" s="1">
         <f t="shared" si="47"/>
-        <v>1856.5498870602394</v>
+        <v>2424.2831288492207</v>
       </c>
       <c r="DM19" s="1">
         <f t="shared" si="47"/>
-        <v>1837.984388189637</v>
+        <v>2400.0402975607285</v>
       </c>
       <c r="DN19" s="1">
         <f t="shared" si="47"/>
-        <v>1819.6045443077405</v>
+        <v>2376.0398945851211</v>
       </c>
       <c r="DO19" s="1">
         <f t="shared" si="47"/>
-        <v>1801.4084988646632</v>
+        <v>2352.27949563927</v>
       </c>
       <c r="DP19" s="1">
         <f t="shared" si="47"/>
-        <v>1783.3944138760166</v>
+        <v>2328.7567006828772</v>
       </c>
       <c r="DQ19" s="1">
         <f t="shared" si="47"/>
-        <v>1765.5604697372564</v>
+        <v>2305.4691336760484</v>
       </c>
       <c r="DR19" s="1">
         <f t="shared" si="47"/>
-        <v>1747.9048650398838</v>
+        <v>2282.4144423392877</v>
       </c>
       <c r="DS19" s="1">
         <f t="shared" si="47"/>
-        <v>1730.4258163894849</v>
+        <v>2259.590297915895</v>
       </c>
       <c r="DT19" s="1">
         <f t="shared" si="47"/>
-        <v>1713.12155822559</v>
+        <v>2236.9943949367362</v>
       </c>
       <c r="DU19" s="1">
         <f t="shared" si="47"/>
-        <v>1695.9903426433341</v>
+        <v>2214.6244509873686</v>
       </c>
       <c r="DV19" s="1">
         <f t="shared" si="47"/>
-        <v>1679.0304392169007</v>
+        <v>2192.478206477495</v>
       </c>
       <c r="DW19" s="1">
         <f t="shared" si="47"/>
-        <v>1662.2401348247317</v>
+        <v>2170.5534244127198</v>
       </c>
       <c r="DX19" s="1">
         <f t="shared" si="47"/>
-        <v>1645.6177334764843</v>
+        <v>2148.8478901685926</v>
       </c>
       <c r="DY19" s="1">
         <f t="shared" si="47"/>
-        <v>1629.1615561417195</v>
+        <v>2127.3594112669066</v>
       </c>
       <c r="DZ19" s="1">
         <f t="shared" si="47"/>
-        <v>1612.8699405803022</v>
+        <v>2106.0858171542377</v>
       </c>
       <c r="EA19" s="1">
         <f t="shared" si="47"/>
-        <v>1596.7412411744992</v>
+        <v>2085.0249589826954</v>
       </c>
       <c r="EB19" s="1">
         <f t="shared" si="47"/>
-        <v>1580.7738287627542</v>
+        <v>2064.1747093928684</v>
       </c>
       <c r="EC19" s="1">
         <f t="shared" si="47"/>
-        <v>1564.9660904751267</v>
+        <v>2043.5329622989398</v>
       </c>
       <c r="ED19" s="1">
         <f t="shared" si="47"/>
-        <v>1549.3164295703755</v>
+        <v>2023.0976326759503</v>
       </c>
       <c r="EE19" s="1">
         <f t="shared" si="47"/>
-        <v>1533.8232652746717</v>
+        <v>2002.8666563491909</v>
       </c>
       <c r="EF19" s="1">
         <f t="shared" si="47"/>
-        <v>1518.485032621925</v>
+        <v>1982.8379897856989</v>
       </c>
       <c r="EG19" s="1">
         <f t="shared" si="47"/>
-        <v>1503.3001822957058</v>
+        <v>1963.0096098878419</v>
       </c>
       <c r="EH19" s="1">
         <f t="shared" si="47"/>
-        <v>1488.2671804727488</v>
+        <v>1943.3795137889633</v>
       </c>
       <c r="EI19" s="1">
         <f t="shared" si="47"/>
-        <v>1473.3845086680212</v>
+        <v>1923.9457186510738</v>
       </c>
       <c r="EJ19" s="1">
         <f t="shared" si="47"/>
-        <v>1458.650663581341</v>
+        <v>1904.7062614645631</v>
       </c>
       <c r="EK19" s="1">
         <f t="shared" si="47"/>
-        <v>1444.0641569455274</v>
+        <v>1885.6591988499174</v>
       </c>
       <c r="EL19" s="1">
         <f t="shared" ref="EL19:FF19" si="48">EK19*(1+$AV$25)</f>
-        <v>1429.6235153760722</v>
+        <v>1866.8026068614181</v>
       </c>
       <c r="EM19" s="1">
         <f t="shared" si="48"/>
-        <v>1415.3272802223114</v>
+        <v>1848.1345807928039</v>
       </c>
       <c r="EN19" s="1">
         <f t="shared" si="48"/>
-        <v>1401.1740074200882</v>
+        <v>1829.6532349848758</v>
       </c>
       <c r="EO19" s="1">
         <f t="shared" si="48"/>
-        <v>1387.1622673458874</v>
+        <v>1811.356702635027</v>
       </c>
       <c r="EP19" s="1">
         <f t="shared" si="48"/>
-        <v>1373.2906446724285</v>
+        <v>1793.2431356086768</v>
       </c>
       <c r="EQ19" s="1">
         <f t="shared" si="48"/>
-        <v>1359.5577382257043</v>
+        <v>1775.3107042525901</v>
       </c>
       <c r="ER19" s="1">
         <f t="shared" si="48"/>
-        <v>1345.9621608434472</v>
+        <v>1757.5575972100642</v>
       </c>
       <c r="ES19" s="1">
         <f t="shared" si="48"/>
-        <v>1332.5025392350128</v>
+        <v>1739.9820212379634</v>
       </c>
       <c r="ET19" s="1">
         <f t="shared" si="48"/>
-        <v>1319.1775138426626</v>
+        <v>1722.5822010255838</v>
       </c>
       <c r="EU19" s="1">
         <f t="shared" si="48"/>
-        <v>1305.9857387042359</v>
+        <v>1705.356379015328</v>
       </c>
       <c r="EV19" s="1">
         <f t="shared" si="48"/>
-        <v>1292.9258813171934</v>
+        <v>1688.3028152251748</v>
       </c>
       <c r="EW19" s="1">
         <f t="shared" si="48"/>
-        <v>1279.9966225040214</v>
+        <v>1671.4197870729231</v>
       </c>
       <c r="EX19" s="1">
         <f t="shared" si="48"/>
-        <v>1267.1966562789812</v>
+        <v>1654.7055892021938</v>
       </c>
       <c r="EY19" s="1">
         <f t="shared" si="48"/>
-        <v>1254.5246897161915</v>
+        <v>1638.1585333101718</v>
       </c>
       <c r="EZ19" s="1">
         <f t="shared" si="48"/>
-        <v>1241.9794428190296</v>
+        <v>1621.77694797707</v>
       </c>
       <c r="FA19" s="1">
         <f t="shared" si="48"/>
-        <v>1229.5596483908394</v>
+        <v>1605.5591784972992</v>
       </c>
       <c r="FB19" s="1">
         <f t="shared" si="48"/>
-        <v>1217.2640519069309</v>
+        <v>1589.5035867123261</v>
       </c>
       <c r="FC19" s="1">
         <f t="shared" si="48"/>
-        <v>1205.0914113878616</v>
+        <v>1573.6085508452029</v>
       </c>
       <c r="FD19" s="1">
         <f t="shared" si="48"/>
-        <v>1193.040497273983</v>
+        <v>1557.8724653367508</v>
       </c>
       <c r="FE19" s="1">
         <f t="shared" si="48"/>
-        <v>1181.1100923012432</v>
+        <v>1542.2937406833832</v>
       </c>
       <c r="FF19" s="1">
         <f t="shared" si="48"/>
-        <v>1169.2989913782308</v>
+        <v>1526.8708032765494</v>
       </c>
     </row>
     <row r="20" spans="2:162" x14ac:dyDescent="0.3">
@@ -3993,11 +3993,11 @@
       </c>
       <c r="X21" s="8">
         <f t="shared" si="55"/>
-        <v>0.61997975580937348</v>
+        <v>1.6973311539976361</v>
       </c>
       <c r="Y21" s="8">
         <f t="shared" si="55"/>
-        <v>-0.15747731390311148</v>
+        <v>1.1679341473020877</v>
       </c>
       <c r="Z21" s="8">
         <f t="shared" si="55"/>
@@ -4030,47 +4030,47 @@
       </c>
       <c r="AI21" s="8">
         <f t="shared" si="56"/>
-        <v>4.8711534856242604</v>
+        <v>7.2739163450177271</v>
       </c>
       <c r="AJ21" s="8">
         <f t="shared" si="56"/>
-        <v>7.9978984126033863</v>
+        <v>10.980725871918079</v>
       </c>
       <c r="AK21" s="8">
         <f t="shared" si="56"/>
-        <v>10.191807625268533</v>
+        <v>13.594180351284127</v>
       </c>
       <c r="AL21" s="8">
         <f t="shared" si="56"/>
-        <v>11.566446456843028</v>
+        <v>15.242456353499522</v>
       </c>
       <c r="AM21" s="8">
         <f t="shared" si="56"/>
-        <v>12.657160688019927</v>
+        <v>16.554287136932444</v>
       </c>
       <c r="AN21" s="8">
         <f t="shared" si="56"/>
-        <v>13.337693210937202</v>
+        <v>17.391297327057341</v>
       </c>
       <c r="AO21" s="8">
         <f t="shared" si="56"/>
-        <v>13.795020021085822</v>
+        <v>17.970548771679493</v>
       </c>
       <c r="AP21" s="8">
         <f t="shared" ref="AP21:AS21" si="57">AP19/AP20</f>
-        <v>14.265213451475299</v>
+        <v>18.566010596674694</v>
       </c>
       <c r="AQ21" s="8">
         <f t="shared" si="57"/>
-        <v>14.484551035480749</v>
+        <v>18.87169818614089</v>
       </c>
       <c r="AR21" s="8">
         <f t="shared" si="57"/>
-        <v>14.704167662568453</v>
+        <v>19.179060428742254</v>
       </c>
       <c r="AS21" s="8">
         <f t="shared" si="57"/>
-        <v>14.926057360724892</v>
+        <v>19.490448003602161</v>
       </c>
     </row>
     <row r="23" spans="2:162" x14ac:dyDescent="0.3">
@@ -4151,11 +4151,11 @@
       </c>
       <c r="X23" s="7">
         <f t="shared" ref="X23" si="72">X5/T5-1</f>
-        <v>-9.9999999999999978E-2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="Y23" s="7">
         <f t="shared" ref="Y23" si="73">Y5/U5-1</f>
-        <v>-0.15000000000000002</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="Z23" s="7">
         <f t="shared" ref="Z23" si="74">Z5/V5-1</f>
@@ -4185,11 +4185,11 @@
       </c>
       <c r="AI23" s="7">
         <f t="shared" si="75"/>
-        <v>-7.175807434491166E-2</v>
+        <v>7.7117611212675241E-2</v>
       </c>
       <c r="AJ23" s="7">
         <f t="shared" si="75"/>
-        <v>0.25</v>
+        <v>0.24999999999999978</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="75"/>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AP24" s="7">
         <f t="shared" ref="AP24:AS24" si="86">AP7/AP5</f>
-        <v>0.8600000000000001</v>
+        <v>0.85999999999999988</v>
       </c>
       <c r="AQ24" s="7">
         <f t="shared" si="86"/>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AR24" s="7">
         <f t="shared" si="86"/>
-        <v>0.85999999999999988</v>
+        <v>0.86</v>
       </c>
       <c r="AS24" s="7">
         <f t="shared" si="86"/>
@@ -4488,11 +4488,11 @@
       </c>
       <c r="X25" s="7">
         <f t="shared" si="91"/>
-        <v>0.15804482462595038</v>
+        <v>0.30353361846946275</v>
       </c>
       <c r="Y25" s="7">
         <f t="shared" si="91"/>
-        <v>-2.5418675933699068E-2</v>
+        <v>0.23607240419719677</v>
       </c>
       <c r="Z25" s="7">
         <f t="shared" si="91"/>
@@ -4525,47 +4525,47 @@
       </c>
       <c r="AI25" s="7">
         <f t="shared" si="92"/>
-        <v>0.25259268863511775</v>
+        <v>0.31919345987383674</v>
       </c>
       <c r="AJ25" s="7">
         <f t="shared" si="92"/>
-        <v>0.34301575255457917</v>
+        <v>0.4020321235608611</v>
       </c>
       <c r="AK25" s="7">
         <f t="shared" si="92"/>
-        <v>0.38047051110242314</v>
+        <v>0.43431000745903109</v>
       </c>
       <c r="AL25" s="7">
         <f t="shared" si="92"/>
-        <v>0.3985042837365701</v>
+        <v>0.44985121081740931</v>
       </c>
       <c r="AM25" s="7">
         <f t="shared" si="92"/>
-        <v>0.41069980716152399</v>
+        <v>0.46036110874360309</v>
       </c>
       <c r="AN25" s="7">
         <f t="shared" si="92"/>
-        <v>0.41580377400975244</v>
+        <v>0.46475962192949871</v>
       </c>
       <c r="AO25" s="7">
         <f t="shared" si="92"/>
-        <v>0.4174369200755183</v>
+        <v>0.46616703986898989</v>
       </c>
       <c r="AP25" s="7">
         <f t="shared" ref="AP25:AS25" si="93">AP13/AP5</f>
-        <v>0.4190542103542379</v>
+        <v>0.46756079355664115</v>
       </c>
       <c r="AQ25" s="7">
         <f t="shared" si="93"/>
-        <v>0.41723085563643014</v>
+        <v>0.4659894569850439</v>
       </c>
       <c r="AR25" s="7">
         <f t="shared" si="93"/>
-        <v>0.41538962489197734</v>
+        <v>0.46440271515294068</v>
       </c>
       <c r="AS25" s="7">
         <f t="shared" si="93"/>
-        <v>0.41353034286571638</v>
+        <v>0.46280041702836583</v>
       </c>
       <c r="AU25" t="s">
         <v>36</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="X27" s="7">
         <f t="shared" si="120"/>
-        <v>0.12</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="120"/>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="AI27" s="7">
         <f t="shared" si="121"/>
-        <v>0.10139350531267133</v>
+        <v>0.10473231308873863</v>
       </c>
       <c r="AJ27" s="7">
         <f t="shared" si="121"/>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="AQ27" s="7">
         <f t="shared" si="122"/>
-        <v>0.09</v>
+        <v>8.9999999999999983E-2</v>
       </c>
       <c r="AR27" s="7">
         <f t="shared" si="122"/>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AV27" s="4">
         <f>NPV(AV26,AH19:FF19)</f>
-        <v>38029.584265022502</v>
+        <v>49292.721511604293</v>
       </c>
     </row>
     <row r="28" spans="2:162" x14ac:dyDescent="0.3">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AI29" s="7">
         <f t="shared" si="150"/>
-        <v>0.15000000000000002</v>
+        <v>0.14999999999999994</v>
       </c>
       <c r="AJ29" s="7">
         <f t="shared" si="150"/>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AN29" s="7">
         <f t="shared" si="150"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AO29" s="7">
         <f t="shared" si="150"/>
@@ -5229,11 +5229,11 @@
       </c>
       <c r="AP29" s="7">
         <f t="shared" ref="AP29:AS29" si="151">AP18/AP17</f>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AQ29" s="7">
         <f t="shared" si="151"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AR29" s="7">
         <f t="shared" si="151"/>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AV29" s="4">
         <f>AV27+AV28</f>
-        <v>42339.384265022498</v>
+        <v>53602.521511604296</v>
       </c>
     </row>
     <row r="30" spans="2:162" x14ac:dyDescent="0.3">
@@ -5341,11 +5341,11 @@
       </c>
       <c r="X30" s="7">
         <f t="shared" si="155"/>
-        <v>0.12065616568555304</v>
+        <v>0.24774212426416473</v>
       </c>
       <c r="Y30" s="7">
         <f t="shared" si="155"/>
-        <v>-3.9030368403584467E-2</v>
+        <v>0.18926860527457939</v>
       </c>
       <c r="Z30" s="7">
         <f t="shared" si="155"/>
@@ -5378,54 +5378,54 @@
       </c>
       <c r="AI30" s="7">
         <f t="shared" si="156"/>
-        <v>0.20298538153744142</v>
+        <v>0.26121571666996696</v>
       </c>
       <c r="AJ30" s="7">
         <f t="shared" si="156"/>
-        <v>0.26662374167779967</v>
+        <v>0.31546562177929904</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="156"/>
-        <v>0.29803639495341927</v>
+        <v>0.34258564771150068</v>
       </c>
       <c r="AL30" s="7">
         <f t="shared" si="156"/>
-        <v>0.31318018782070733</v>
+        <v>0.35567008765960983</v>
       </c>
       <c r="AM30" s="7">
         <f t="shared" si="156"/>
-        <v>0.3233141833229134</v>
+        <v>0.36441563385211284</v>
       </c>
       <c r="AN30" s="7">
         <f t="shared" si="156"/>
-        <v>0.32759393113789176</v>
+        <v>0.36811639245603983</v>
       </c>
       <c r="AO30" s="7">
         <f t="shared" si="156"/>
-        <v>0.32895783469372181</v>
+        <v>0.36929828607041548</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" ref="AP30:AS30" si="157">AP19/AP5</f>
-        <v>0.33026226034237383</v>
+        <v>0.3704224687767646</v>
       </c>
       <c r="AQ30" s="7">
         <f t="shared" si="157"/>
-        <v>0.32876497296595031</v>
+        <v>0.36913866599102152</v>
       </c>
       <c r="AR30" s="7">
         <f t="shared" si="157"/>
-        <v>0.32720563705977701</v>
+        <v>0.36779490766170631</v>
       </c>
       <c r="AS30" s="7">
         <f t="shared" si="157"/>
-        <v>0.32563064202321612</v>
+        <v>0.36643760370765865</v>
       </c>
       <c r="AU30" t="s">
         <v>41</v>
       </c>
       <c r="AV30" s="5">
         <f>AV29/AO20</f>
-        <v>166.75614125648877</v>
+        <v>211.11666605594448</v>
       </c>
     </row>
     <row r="31" spans="2:162" x14ac:dyDescent="0.3">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AV31" s="5">
         <f>Main!D3</f>
-        <v>170.76</v>
+        <v>269.39999999999998</v>
       </c>
     </row>
     <row r="32" spans="2:162" x14ac:dyDescent="0.3">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AV32" s="10">
         <f>AV30/AV31-1</f>
-        <v>-2.3447287090133662E-2</v>
+        <v>-0.2163449663847643</v>
       </c>
     </row>
     <row r="33" spans="47:48" x14ac:dyDescent="0.3">
